--- a/artfynd/A 46072-2020 artfynd.xlsx
+++ b/artfynd/A 46072-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118079754</v>
+        <v>118079753</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456227</v>
+        <v>456207</v>
       </c>
       <c r="R2" t="n">
-        <v>6648052</v>
+        <v>6648042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118079757</v>
+        <v>118079754</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>78569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456258</v>
+        <v>456227</v>
       </c>
       <c r="R3" t="n">
-        <v>6648028</v>
+        <v>6648052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118079753</v>
+        <v>118079752</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456207</v>
+        <v>456209</v>
       </c>
       <c r="R4" t="n">
-        <v>6648042</v>
+        <v>6648044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,21 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118079751</v>
+        <v>118079757</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>97753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456169</v>
+        <v>456258</v>
       </c>
       <c r="R5" t="n">
-        <v>6648043</v>
+        <v>6648028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,21 +1082,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1230,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118079752</v>
+        <v>118079751</v>
       </c>
       <c r="B7" t="n">
-        <v>97753</v>
+        <v>90464</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456209</v>
+        <v>456169</v>
       </c>
       <c r="R7" t="n">
-        <v>6648044</v>
+        <v>6648043</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,6 +1301,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 46072-2020 artfynd.xlsx
+++ b/artfynd/A 46072-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118079753</v>
+        <v>118079752</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456207</v>
+        <v>456209</v>
       </c>
       <c r="R2" t="n">
-        <v>6648042</v>
+        <v>6648044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118079754</v>
+        <v>118079751</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
+        <v>90466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456227</v>
+        <v>456169</v>
       </c>
       <c r="R3" t="n">
-        <v>6648052</v>
+        <v>6648043</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +863,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118079752</v>
+        <v>118079754</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>78571</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456209</v>
+        <v>456227</v>
       </c>
       <c r="R4" t="n">
-        <v>6648044</v>
+        <v>6648052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>118079757</v>
       </c>
       <c r="B5" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118079749</v>
+        <v>118079753</v>
       </c>
       <c r="B6" t="n">
-        <v>90464</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456152</v>
+        <v>456207</v>
       </c>
       <c r="R6" t="n">
-        <v>6648047</v>
+        <v>6648042</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118079751</v>
+        <v>118079749</v>
       </c>
       <c r="B7" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456169</v>
+        <v>456152</v>
       </c>
       <c r="R7" t="n">
-        <v>6648043</v>
+        <v>6648047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
